--- a/nr-update-fr-core-1/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
+++ b/nr-update-fr-core-1/ig/StructureDefinition-fr-core-patient-contact-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T11:01:45+00:00</t>
+    <t>2026-02-23T12:41:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
